--- a/docs/密度增益标定-现场访谈提纲.xlsx
+++ b/docs/密度增益标定-现场访谈提纲.xlsx
@@ -12,6 +12,7 @@
     <sheet name="补充问题（10 分钟）" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="答案记录区" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="答案怎么进系统" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="访谈结论（2026-09-12）" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1007,10 +1008,26 @@
           <t>偏 0.15 / 0.30 / 0.60% 各调多少</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr"/>
-      <c r="D4" s="10" t="inlineStr"/>
-      <c r="E4" s="10" t="inlineStr"/>
-      <c r="F4" s="10" t="inlineStr"/>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>0.01 / 0.02 / 最多 0.03（大多数是 0.01、0.02）</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>现场专家（经用户转述）</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>⇒ 口径 = 比例律 15%/单位 + **封顶 0.03**；旧表斜率 0.1 且无上限（1.5% 偏差会给 0.145 = 4.8 倍）已被替换</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -1023,10 +1040,26 @@
           <t>0.15% 的口径：总灰分 or 重介灰分</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr"/>
-      <c r="D5" s="10" t="inlineStr"/>
-      <c r="E5" s="10" t="inlineStr"/>
-      <c r="F5" s="10" t="inlineStr"/>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>总灰分</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>现场专家（经用户转述）</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>⇒ 现有实现口径正确，无需改换算；0.867 仅用于「重介版」换算</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
@@ -1039,10 +1072,26 @@
           <t>密度最小可设步长（0.005 / 0.01）</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr"/>
-      <c r="D6" s="10" t="inlineStr"/>
-      <c r="E6" s="10" t="inlineStr"/>
-      <c r="F6" s="10" t="inlineStr"/>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>0.005 甚至更小</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>现场专家（经用户转述）</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>⇒ 执行器分辨率足够细；死区 0.05 与增益 15%/单位相容（半步响应 0.5×15×0.005=0.0375 &lt; 0.05），不必放宽</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
@@ -1342,4 +1391,152 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="66" customWidth="1" min="2" max="2"/>
+    <col width="76" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>访谈结论与由此产生的口径变更（2026-09-12）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>项</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>答案 / 结论</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>对系统做了什么</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Q1 答案</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>偏差 0.15% → 0.01；0.30% → 0.02；更大时**最多 0.03**（大多数是 0.01、0.02）</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>专家表改为 Δρ = min(|ΔA| / 15, 0.03)（死区 0.05 不变）。旧表（0.15→0.01、0.25→0.02、斜率 0.1 无上限）已替换：它在 1.5% 偏差时给 0.145，是现场上限的 4.8 倍。前后端同步修改，简报 golden 已按前端重新生成并对拍通过。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Q1 的判别结果</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>既不是纯「增益律」也不是纯「步长限幅」：**小偏差按比例（≈1/15 g/cm³ 每 1% 灰分）、大偏差封顶 0.03**</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>⇒ 表的斜率取现场的 0.067（=1/15），而不是旧表的 0.1；并显式引入上限 0.03。实验（P3）要标的正是这条比例律的增益到底是不是 15%/单位。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Q2 答案</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>口径 = **总精煤灰分**</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>现有实现（deltaA 按总灰分、重介版先换算等效总灰分）**无需改动**；0.867 换算系数只影响「重介版」显示。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Q3 答案</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>密度最小可设 **0.005 甚至更小**</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>执行器分辨率不再构成限制：死区 0.05 与增益 15%/单位相容（半个最小步的响应 = 0.5×15×0.005 = 0.0375 &lt; 0.05），无需为抗极限环放宽死区。另：逐步建议的步长上限目前取界面「钳制」（默认 0.01），现场上限是 0.03 —— 是否放宽见下条。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>仍待定（1 项）</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>系统发布的**单次建议步长上限**取多少：0.01（现默认，3 步走完 0.03）、0.02（覆盖「大多数」情形）还是 0.03（与现场上限一致）</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>现为 0.01（最保守）。现场做法允许一次 0.03；在真实增益尚未实测（P3 未做）之前，建议先保持 0.01 或放到 0.02，等阶跃实验给出增益置信区间后再放到 0.03。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>下一步</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>① 按 P3 做受控阶跃，验证增益是否 ≈15%/单位（若显著更大，说明现场这条比例律本身偏猛）；② 之后按 P4 影子运行 → 收缩合并上线；③ PLC/501 接入后彻底停用仿真项</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>见 docs/密度阶跃实验-设计与验收.xlsx</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>